--- a/diseases/d071/2015-2019.xlsx
+++ b/diseases/d071/2015-2019.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">

--- a/diseases/d071/2015-2019.xlsx
+++ b/diseases/d071/2015-2019.xlsx
@@ -769,11 +769,11 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1812863009903253</v>
+        <v>0.1829735552246143</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -1165,11 +1165,11 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1553575609830168</v>
+        <v>0.1568034931972297</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1561,11 +1561,11 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1944655500548136</v>
+        <v>0.1962754652053844</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1957,11 +1957,11 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1903828478989666</v>
+        <v>0.1921547648309067</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2353,11 +2353,11 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1762008298839195</v>
+        <v>0.1778407530037737</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -2749,11 +2749,11 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1809281692222685</v>
+        <v>0.1826120902794847</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -3541,11 +3541,11 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1830053334769977</v>
+        <v>0.1847085869612365</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -3937,11 +3937,11 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0.184509486902836</v>
+        <v>0.1862267397307809</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -4333,11 +4333,11 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1760575771766968</v>
+        <v>0.1776961670257219</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -4729,11 +4729,11 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1721181277280726</v>
+        <v>0.173720052629296</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5125,11 +5125,11 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1587239996027502</v>
+        <v>0.1602012636814482</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -5917,11 +5917,11 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1612309219791475</v>
+        <v>0.1627315182973555</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -6313,11 +6313,11 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1360347864794288</v>
+        <v>0.1371811077913123</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -6709,11 +6709,11 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1457210330559745</v>
+        <v>0.14694897724661</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7105,11 +7105,11 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1772725568310462</v>
+        <v>0.1787663755458515</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -7501,11 +7501,11 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1591820669013211</v>
+        <v>0.1605234428866927</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -7897,11 +7897,11 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1527720507844894</v>
+        <v>0.1540594116295105</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -8293,11 +8293,11 @@
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1429433594053474</v>
+        <v>0.1441478970351643</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -8689,11 +8689,11 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1456498106546764</v>
+        <v>0.1468771546770857</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -9085,11 +9085,11 @@
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0.1599655133156005</v>
+        <v>0.1613134911514594</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -9481,11 +9481,11 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1524159387779987</v>
+        <v>0.1537002987818892</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -9877,11 +9877,11 @@
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0.1263485399028831</v>
+        <v>0.1274132383360147</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -10273,11 +10273,11 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.1314053303950503</v>
+        <v>0.1325126407722363</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -10669,11 +10669,11 @@
         <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0.1294111031587027</v>
+        <v>0.1305016088255573</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -11065,11 +11065,11 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.120366361757502</v>
+        <v>0.1214190313618216</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -11461,11 +11461,11 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.1336066615508272</v>
+        <v>0.134775124811622</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -11857,11 +11857,11 @@
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.1408994469984876</v>
+        <v>0.1421316896529558</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -12253,11 +12253,11 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0.1254642311966433</v>
+        <v>0.1265614844547928</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -12649,11 +12649,11 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.1207911842107638</v>
+        <v>0.1218475691195692</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -13045,11 +13045,11 @@
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.1350935401372434</v>
+        <v>0.1362750069637386</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -13441,11 +13441,11 @@
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.1231277077037035</v>
+        <v>0.124204526787181</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -13837,11 +13837,11 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.1261722686187462</v>
+        <v>0.1272757140510389</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -14233,11 +14233,11 @@
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.1245437825479094</v>
+        <v>0.125632985979673</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -14629,11 +14629,11 @@
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.1166845671625667</v>
+        <v>0.1177050374613423</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15025,11 +15025,11 @@
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0.1239065488680168</v>
+        <v>0.1249901793430516</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -15421,11 +15421,11 @@
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0.1104538378480607</v>
+        <v>0.1114198170143774</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -15817,11 +15817,11 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.1045095588529887</v>
+        <v>0.1055208088742787</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -16213,11 +16213,11 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0.0888648372984617</v>
+        <v>0.08972470666922819</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -16609,11 +16609,11 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.1181106005648072</v>
+        <v>0.1192534562867775</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -17005,11 +17005,11 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.1082445599448352</v>
+        <v>0.1092919503917006</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -17401,11 +17401,11 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.1185334308770916</v>
+        <v>0.1196803779679951</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -17797,11 +17797,11 @@
         <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>0.1007040860424281</v>
+        <v>0.1016785137433205</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -18193,11 +18193,11 @@
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.1104996549436859</v>
+        <v>0.1115688660248611</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -18589,11 +18589,11 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.1070465407266957</v>
+        <v>0.1080823389615842</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -18985,11 +18985,11 @@
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.09372738588973359</v>
+        <v>0.09463430600323038</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -19381,11 +19381,11 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.09267031010902231</v>
+        <v>0.09356700180018641</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -19777,11 +19777,11 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.08660974229961096</v>
+        <v>0.08744779103606777</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -20173,11 +20173,11 @@
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.084988892769187</v>
+        <v>0.08581125792473371</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -20569,11 +20569,11 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.08900469833990414</v>
+        <v>0.08985305798252582</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -20965,11 +20965,11 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0.07312856430295203</v>
+        <v>0.07382559854760014</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -21361,11 +21361,11 @@
         <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>0.09406258174990659</v>
+        <v>0.09495915125382957</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -21757,11 +21757,11 @@
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.09638077831282436</v>
+        <v>0.09729944400317714</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -22153,11 +22153,11 @@
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.09490556231824032</v>
+        <v>0.09581016679904686</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -22549,11 +22549,11 @@
         <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0.08422780845267962</v>
+        <v>0.08503063655962782</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -22945,11 +22945,11 @@
         <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>0.09343034632365628</v>
+        <v>0.09432088959491659</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -23341,11 +23341,11 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.08654600501559739</v>
+        <v>0.08737092930897537</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -23737,11 +23737,11 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.07804595095156551</v>
+        <v>0.07878985589470101</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -24133,11 +24133,11 @@
         <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0.0787484347585103</v>
+        <v>0.07949903551571542</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -24529,11 +24529,11 @@
         <v>1</v>
       </c>
       <c r="R122" t="n">
-        <v>0.07235583211531277</v>
+        <v>0.07304550096448428</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -24925,11 +24925,11 @@
         <v>2</v>
       </c>
       <c r="R124" t="n">
-        <v>0.07151285154697902</v>
+        <v>0.072194485419267</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">

--- a/diseases/d071/2015-2019.xlsx
+++ b/diseases/d071/2015-2019.xlsx
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">

--- a/diseases/d071/2015-2019.xlsx
+++ b/diseases/d071/2015-2019.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
